--- a/docs/培训/OpenWorker培训/02-交期风险/排产计划.xlsx
+++ b/docs/培训/OpenWorker培训/02-交期风险/排产计划.xlsx
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46263</v>
+        <v>46268</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46263</v>
+        <v>46268</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46263</v>
+        <v>46268</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>46263</v>
+        <v>46268</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46279</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>46279</v>
+        <v>46284</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>46283</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>46283</v>
+        <v>46288</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>46298</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>46257</v>
+        <v>46262</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>46264</v>
+        <v>46269</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>46264</v>
+        <v>46269</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>46279</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>46279</v>
+        <v>46284</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>46286</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>46286</v>
+        <v>46291</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>46301</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>46283</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>46283</v>
+        <v>46288</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>46280</v>
+        <v>46285</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>46280</v>
+        <v>46285</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>46286</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>46286</v>
+        <v>46291</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>46299</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>46299</v>
+        <v>46304</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>46298</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>46298</v>
+        <v>46303</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>46313</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>46280</v>
+        <v>46285</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>46280</v>
+        <v>46285</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>46314</v>
+        <v>46319</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>46314</v>
+        <v>46319</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>46322</v>
+        <v>46327</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>46277</v>
+        <v>46282</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>46327</v>
+        <v>46332</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>46327</v>
+        <v>46332</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>46337</v>
+        <v>46342</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>46329</v>
+        <v>46334</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>46329</v>
+        <v>46334</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>46340</v>
+        <v>46345</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>46340</v>
+        <v>46345</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>46352</v>
+        <v>46357</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>46245</v>
+        <v>46250</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>46245</v>
+        <v>46250</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>46264</v>
+        <v>46269</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>46264</v>
+        <v>46269</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>46250</v>
+        <v>46255</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>46250</v>
+        <v>46255</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
